--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>122645747</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122645698</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>122650339</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>123107459</v>
       </c>
       <c r="B43" t="n">
-        <v>57491</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>123113132</v>
       </c>
       <c r="B47" t="n">
-        <v>57491</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>391091</v>
+        <v>125014705</v>
       </c>
       <c r="B25" t="n">
-        <v>81235</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,41 +3272,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810860.7270867341</v>
+        <v>810458</v>
       </c>
       <c r="R25" t="n">
-        <v>7171669.623737417</v>
+        <v>7171462</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,22 +3338,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,6 +3352,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3372,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2055139</v>
+        <v>125014666</v>
       </c>
       <c r="B26" t="n">
-        <v>78097</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,41 +3383,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810860.7270867341</v>
+        <v>810442</v>
       </c>
       <c r="R26" t="n">
-        <v>7171669.623737417</v>
+        <v>7171466</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3442,22 +3449,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,10 +3463,10 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AR26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3478,17 +3475,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>292476</v>
+        <v>125014750</v>
       </c>
       <c r="B27" t="n">
-        <v>79432</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,41 +3494,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tallskog Storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810917.5546458759</v>
+        <v>810464</v>
       </c>
       <c r="R27" t="n">
-        <v>7171682.39060352</v>
+        <v>7171463</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3555,27 +3560,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2007-10-31</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rapport från Patrik Nygren, SNF</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3584,28 +3574,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>292265</v>
+        <v>125014622</v>
       </c>
       <c r="B28" t="n">
-        <v>79432</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,41 +3605,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810860.7270867341</v>
+        <v>810448</v>
       </c>
       <c r="R28" t="n">
-        <v>7171669.623737417</v>
+        <v>7171471</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3672,22 +3671,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3696,10 +3690,10 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AR28" t="inlineStr"/>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3708,17 +3702,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650329</v>
+        <v>391091</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>81235</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3731,44 +3725,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810886</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R29" t="n">
-        <v>7171642</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,12 +3779,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3806,7 +3803,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3825,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122650264</v>
+        <v>2055139</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>78097</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,44 +3837,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811045</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R30" t="n">
-        <v>7171680</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3902,12 +3891,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3916,10 +3915,10 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AR30" t="inlineStr"/>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -3935,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650270</v>
+        <v>292476</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79432</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3951,44 +3950,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>Tallskog Storön, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811036</v>
+        <v>810917.5546458759</v>
       </c>
       <c r="R31" t="n">
-        <v>7171698</v>
+        <v>7171682.39060352</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4012,12 +4004,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-10-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>rapport från Patrik Nygren, SNF</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4026,29 +4033,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Via Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650066</v>
+        <v>292265</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79432</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4061,44 +4067,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810939</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R32" t="n">
-        <v>7171504</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4122,12 +4121,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4136,10 +4145,10 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AR32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
@@ -4155,7 +4164,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122649988</v>
+        <v>122650329</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4202,10 +4211,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810939</v>
+        <v>810886</v>
       </c>
       <c r="R33" t="n">
-        <v>7171498</v>
+        <v>7171642</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4265,7 +4274,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122649921</v>
+        <v>122650264</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4312,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810786</v>
+        <v>811045</v>
       </c>
       <c r="R34" t="n">
-        <v>7171426</v>
+        <v>7171680</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4375,10 +4384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650277</v>
+        <v>122650270</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,31 +4400,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4423,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811014</v>
+        <v>811036</v>
       </c>
       <c r="R35" t="n">
-        <v>7171734</v>
+        <v>7171698</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,17 +4469,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4490,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650339</v>
+        <v>122650066</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,27 +4510,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4534,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810833</v>
+        <v>810939</v>
       </c>
       <c r="R36" t="n">
-        <v>7171605</v>
+        <v>7171504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4572,17 +4579,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4601,7 +4604,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122649892</v>
+        <v>122649988</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4648,10 +4651,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810633</v>
+        <v>810939</v>
       </c>
       <c r="R37" t="n">
-        <v>7171420</v>
+        <v>7171498</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4711,7 +4714,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122650292</v>
+        <v>122649921</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4758,10 +4761,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810931</v>
+        <v>810786</v>
       </c>
       <c r="R38" t="n">
-        <v>7171669</v>
+        <v>7171426</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4821,10 +4824,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122650350</v>
+        <v>122650277</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4837,30 +4840,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4868,10 +4872,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>810833</v>
+        <v>811014</v>
       </c>
       <c r="R39" t="n">
-        <v>7171605</v>
+        <v>7171734</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4906,13 +4910,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4931,10 +4939,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122649934</v>
+        <v>122650339</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4967,11 +4975,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4979,10 +4983,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810828</v>
+        <v>810833</v>
       </c>
       <c r="R40" t="n">
-        <v>7171441</v>
+        <v>7171605</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5019,7 +5023,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>äldre ringhack i gran</t>
+          <t>barksprätt på gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5046,10 +5050,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122650318</v>
+        <v>122649892</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5062,31 +5066,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5094,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810936</v>
+        <v>810633</v>
       </c>
       <c r="R41" t="n">
-        <v>7171645</v>
+        <v>7171420</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5132,17 +5135,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>två stora bohål i ihålig gammeltall</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5161,10 +5160,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123105448</v>
+        <v>122650292</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5200,11 +5199,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5212,10 +5207,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810833</v>
+        <v>810931</v>
       </c>
       <c r="R42" t="n">
-        <v>7171608</v>
+        <v>7171669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5242,17 +5237,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,10 +5270,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123107459</v>
+        <v>122650350</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5296,31 +5286,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5328,10 +5317,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811055</v>
+        <v>810833</v>
       </c>
       <c r="R43" t="n">
-        <v>7171672</v>
+        <v>7171605</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5358,17 +5347,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5377,6 +5361,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5395,10 +5380,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123105526</v>
+        <v>122649934</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5411,30 +5396,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5442,10 +5428,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810798</v>
+        <v>810828</v>
       </c>
       <c r="R44" t="n">
-        <v>7171573</v>
+        <v>7171441</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5472,12 +5458,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5486,7 +5477,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5505,10 +5495,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107351</v>
+        <v>122650318</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5521,32 +5511,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5556,10 +5543,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811003</v>
+        <v>810936</v>
       </c>
       <c r="R45" t="n">
-        <v>7171721</v>
+        <v>7171645</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5586,17 +5573,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>två stora bohål i ihålig gammeltall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5605,7 +5592,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5624,7 +5610,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123113230</v>
+        <v>123105448</v>
       </c>
       <c r="B46" t="n">
         <v>78788</v>
@@ -5663,7 +5649,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5671,10 +5661,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810850</v>
+        <v>810833</v>
       </c>
       <c r="R46" t="n">
-        <v>7171671</v>
+        <v>7171608</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5707,6 +5697,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5734,7 +5729,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123113132</v>
+        <v>123107459</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810895</v>
+        <v>811055</v>
       </c>
       <c r="R47" t="n">
-        <v>7171694</v>
+        <v>7171672</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5822,7 +5817,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5844,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123113205</v>
+        <v>123105526</v>
       </c>
       <c r="B48" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5865,21 +5860,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5896,10 +5891,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810862</v>
+        <v>810798</v>
       </c>
       <c r="R48" t="n">
-        <v>7171664</v>
+        <v>7171573</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5959,7 +5954,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107500</v>
+        <v>123107351</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -5998,7 +5993,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6006,10 +6005,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811043</v>
+        <v>811003</v>
       </c>
       <c r="R49" t="n">
-        <v>7171704</v>
+        <v>7171721</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6042,6 +6041,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6069,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123113317</v>
+        <v>123113230</v>
       </c>
       <c r="B50" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6085,31 +6089,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6117,10 +6120,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810707</v>
+        <v>810850</v>
       </c>
       <c r="R50" t="n">
-        <v>7171592</v>
+        <v>7171671</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6155,17 +6158,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>hål i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6184,10 +6183,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123107487</v>
+        <v>123113132</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6200,30 +6199,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811052</v>
+        <v>810895</v>
       </c>
       <c r="R51" t="n">
-        <v>7171679</v>
+        <v>7171694</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>rikligt med hänglavar bla garnlav</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6280,7 +6280,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6299,10 +6298,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123113174</v>
+        <v>123113205</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6315,21 +6314,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6346,10 +6345,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810865</v>
+        <v>810862</v>
       </c>
       <c r="R52" t="n">
-        <v>7171668</v>
+        <v>7171664</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6382,11 +6381,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6414,10 +6408,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123105541</v>
+        <v>123107500</v>
       </c>
       <c r="B53" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6426,25 +6420,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6461,10 +6455,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810786</v>
+        <v>811043</v>
       </c>
       <c r="R53" t="n">
-        <v>7171568</v>
+        <v>7171704</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6524,7 +6518,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107426</v>
+        <v>123113317</v>
       </c>
       <c r="B54" t="n">
         <v>57507</v>
@@ -6560,7 +6554,11 @@
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6568,10 +6566,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811024</v>
+        <v>810707</v>
       </c>
       <c r="R54" t="n">
-        <v>7171733</v>
+        <v>7171592</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6608,7 +6606,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6635,10 +6633,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107409</v>
+        <v>123107487</v>
       </c>
       <c r="B55" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6651,31 +6649,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6683,10 +6680,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811024</v>
+        <v>811052</v>
       </c>
       <c r="R55" t="n">
-        <v>7171733</v>
+        <v>7171679</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6723,7 +6720,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6732,6 +6729,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6750,10 +6748,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123107511</v>
+        <v>123113174</v>
       </c>
       <c r="B56" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6762,25 +6760,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6797,10 +6795,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811066</v>
+        <v>810865</v>
       </c>
       <c r="R56" t="n">
-        <v>7171715</v>
+        <v>7171668</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6833,6 +6831,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6860,7 +6863,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107538</v>
+        <v>123105541</v>
       </c>
       <c r="B57" t="n">
         <v>78812</v>
@@ -6907,10 +6910,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810978</v>
+        <v>810786</v>
       </c>
       <c r="R57" t="n">
-        <v>7171744</v>
+        <v>7171568</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6970,7 +6973,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123113295</v>
+        <v>123107426</v>
       </c>
       <c r="B58" t="n">
         <v>57507</v>
@@ -7006,11 +7009,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7018,10 +7017,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810851</v>
+        <v>811024</v>
       </c>
       <c r="R58" t="n">
-        <v>7171663</v>
+        <v>7171733</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7058,7 +7057,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7085,10 +7084,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107589</v>
+        <v>123107409</v>
       </c>
       <c r="B59" t="n">
-        <v>82575</v>
+        <v>57491</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7101,30 +7100,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810886</v>
+        <v>811024</v>
       </c>
       <c r="R59" t="n">
-        <v>7171705</v>
+        <v>7171733</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7170,13 +7170,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7195,7 +7199,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123107525</v>
+        <v>123107511</v>
       </c>
       <c r="B60" t="n">
         <v>78812</v>
@@ -7242,10 +7246,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811018</v>
+        <v>811066</v>
       </c>
       <c r="R60" t="n">
-        <v>7171753</v>
+        <v>7171715</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7305,10 +7309,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123105488</v>
+        <v>123107538</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7317,25 +7321,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7352,10 +7356,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>810824</v>
+        <v>810978</v>
       </c>
       <c r="R61" t="n">
-        <v>7171598</v>
+        <v>7171744</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,11 +7392,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7420,7 +7419,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123107271</v>
+        <v>123113295</v>
       </c>
       <c r="B62" t="n">
         <v>57507</v>
@@ -7468,10 +7467,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810992</v>
+        <v>810851</v>
       </c>
       <c r="R62" t="n">
-        <v>7171739</v>
+        <v>7171663</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7535,10 +7534,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123107580</v>
+        <v>123107589</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7551,27 +7550,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -7642,6 +7641,682 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>123107525</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78812</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>811018</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7171753</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>123105488</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>810824</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7171598</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>123107271</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>810992</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7171739</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>123107580</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>810886</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7171705</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125014301</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>810839</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7171616</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125014526</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78834</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>810999</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7171690</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014705</v>
+        <v>125014750</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810458</v>
+        <v>810464</v>
       </c>
       <c r="R25" t="n">
-        <v>7171462</v>
+        <v>7171463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014666</v>
+        <v>125014622</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810442</v>
+        <v>810448</v>
       </c>
       <c r="R26" t="n">
-        <v>7171466</v>
+        <v>7171471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,6 +3455,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,7 +3487,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014750</v>
+        <v>125014666</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3530,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810464</v>
+        <v>810442</v>
       </c>
       <c r="R27" t="n">
-        <v>7171463</v>
+        <v>7171466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014622</v>
+        <v>125014705</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3641,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810448</v>
+        <v>810458</v>
       </c>
       <c r="R28" t="n">
-        <v>7171471</v>
+        <v>7171462</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,11 +3684,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014750</v>
+        <v>125014666</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810464</v>
+        <v>810442</v>
       </c>
       <c r="R25" t="n">
-        <v>7171463</v>
+        <v>7171466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014666</v>
+        <v>125014705</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810442</v>
+        <v>810458</v>
       </c>
       <c r="R27" t="n">
-        <v>7171466</v>
+        <v>7171462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3591,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014705</v>
+        <v>125014750</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810458</v>
+        <v>810464</v>
       </c>
       <c r="R28" t="n">
-        <v>7171462</v>
+        <v>7171463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3371,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R26" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,11 +3457,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,14 +3475,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3535,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R27" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,6 +3568,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3591,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014750</v>
+        <v>125014705</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810464</v>
+        <v>810458</v>
       </c>
       <c r="R28" t="n">
-        <v>7171463</v>
+        <v>7171462</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -8094,10 +8094,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014301</v>
+        <v>125014526</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78834</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8106,35 +8106,34 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8142,10 +8141,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810839</v>
+        <v>810999</v>
       </c>
       <c r="R68" t="n">
-        <v>7171616</v>
+        <v>7171690</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8180,11 +8179,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8203,17 +8197,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014526</v>
+        <v>125014301</v>
       </c>
       <c r="B69" t="n">
-        <v>78834</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8222,34 +8216,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8257,10 +8252,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810999</v>
+        <v>810839</v>
       </c>
       <c r="R69" t="n">
-        <v>7171690</v>
+        <v>7171616</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8295,6 +8290,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014666</v>
+        <v>125014705</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810442</v>
+        <v>810458</v>
       </c>
       <c r="R25" t="n">
-        <v>7171466</v>
+        <v>7171462</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,14 +3364,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014750</v>
+        <v>125014666</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810464</v>
+        <v>810442</v>
       </c>
       <c r="R26" t="n">
-        <v>7171463</v>
+        <v>7171466</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,14 +3475,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R27" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,11 +3568,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3591,14 +3586,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R28" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3684,6 +3679,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014526</v>
+        <v>125014301</v>
       </c>
       <c r="B68" t="n">
-        <v>78834</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8106,34 +8106,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8141,10 +8142,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810999</v>
+        <v>810839</v>
       </c>
       <c r="R68" t="n">
-        <v>7171690</v>
+        <v>7171616</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8179,6 +8180,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8197,17 +8203,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014301</v>
+        <v>125014526</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78834</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8216,35 +8222,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8252,10 +8257,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810839</v>
+        <v>810999</v>
       </c>
       <c r="R69" t="n">
-        <v>7171616</v>
+        <v>7171690</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8290,11 +8295,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014705</v>
+        <v>125014666</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810458</v>
+        <v>810442</v>
       </c>
       <c r="R25" t="n">
-        <v>7171462</v>
+        <v>7171466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,14 +3364,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014666</v>
+        <v>125014750</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810442</v>
+        <v>810464</v>
       </c>
       <c r="R26" t="n">
-        <v>7171466</v>
+        <v>7171463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,14 +3475,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014750</v>
+        <v>125014705</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810464</v>
+        <v>810458</v>
       </c>
       <c r="R27" t="n">
-        <v>7171463</v>
+        <v>7171462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014666</v>
+        <v>125014622</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810442</v>
+        <v>810448</v>
       </c>
       <c r="R25" t="n">
-        <v>7171466</v>
+        <v>7171471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,6 +3344,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,7 +3376,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014750</v>
+        <v>125014705</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810464</v>
+        <v>810458</v>
       </c>
       <c r="R26" t="n">
-        <v>7171463</v>
+        <v>7171462</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,7 +3487,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014705</v>
+        <v>125014666</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3530,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810458</v>
+        <v>810442</v>
       </c>
       <c r="R27" t="n">
-        <v>7171462</v>
+        <v>7171466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3641,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R28" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,11 +3684,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014622</v>
+        <v>125014705</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810448</v>
+        <v>810458</v>
       </c>
       <c r="R25" t="n">
-        <v>7171471</v>
+        <v>7171462</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,11 +3346,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3369,14 +3364,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3424,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R26" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,6 +3457,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R25" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,6 +3346,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3364,14 +3369,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R26" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,11 +3462,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014750</v>
+        <v>125014705</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810464</v>
+        <v>810458</v>
       </c>
       <c r="R28" t="n">
-        <v>7171463</v>
+        <v>7171462</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -8094,10 +8094,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014301</v>
+        <v>125014526</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78834</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8106,35 +8106,34 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8142,10 +8141,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810839</v>
+        <v>810999</v>
       </c>
       <c r="R68" t="n">
-        <v>7171616</v>
+        <v>7171690</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8180,11 +8179,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8203,17 +8197,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014526</v>
+        <v>125014301</v>
       </c>
       <c r="B69" t="n">
-        <v>78834</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8222,34 +8216,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8257,10 +8252,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810999</v>
+        <v>810839</v>
       </c>
       <c r="R69" t="n">
-        <v>7171690</v>
+        <v>7171616</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8295,6 +8290,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014622</v>
+        <v>125014666</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810448</v>
+        <v>810442</v>
       </c>
       <c r="R25" t="n">
-        <v>7171471</v>
+        <v>7171466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,11 +3344,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014750</v>
+        <v>125014622</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3424,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810464</v>
+        <v>810448</v>
       </c>
       <c r="R26" t="n">
-        <v>7171463</v>
+        <v>7171471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,6 +3457,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014666</v>
+        <v>125014705</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810442</v>
+        <v>810458</v>
       </c>
       <c r="R27" t="n">
-        <v>7171466</v>
+        <v>7171462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3591,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014705</v>
+        <v>125014750</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810458</v>
+        <v>810464</v>
       </c>
       <c r="R28" t="n">
-        <v>7171462</v>
+        <v>7171463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -8094,10 +8094,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014526</v>
+        <v>125014301</v>
       </c>
       <c r="B68" t="n">
-        <v>78834</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8106,34 +8106,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8141,10 +8142,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810999</v>
+        <v>810839</v>
       </c>
       <c r="R68" t="n">
-        <v>7171690</v>
+        <v>7171616</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8179,6 +8180,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8197,17 +8203,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014301</v>
+        <v>125014526</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78834</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8216,35 +8222,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8252,10 +8257,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810839</v>
+        <v>810999</v>
       </c>
       <c r="R69" t="n">
-        <v>7171616</v>
+        <v>7171690</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8290,11 +8295,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>122645747</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122645698</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014666</v>
+        <v>125014750</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810442</v>
+        <v>810464</v>
       </c>
       <c r="R25" t="n">
-        <v>7171466</v>
+        <v>7171463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,17 +3364,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014622</v>
+        <v>125014705</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810448</v>
+        <v>810458</v>
       </c>
       <c r="R26" t="n">
-        <v>7171471</v>
+        <v>7171462</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,11 +3457,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,17 +3475,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3535,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R27" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,6 +3568,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3591,17 +3591,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014750</v>
+        <v>125014666</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810464</v>
+        <v>810442</v>
       </c>
       <c r="R28" t="n">
-        <v>7171463</v>
+        <v>7171466</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4942,7 +4942,7 @@
         <v>122650339</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>123107459</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>123113132</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -8094,10 +8094,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014301</v>
+        <v>125014526</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78971</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8106,35 +8106,34 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8142,10 +8141,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810839</v>
+        <v>810999</v>
       </c>
       <c r="R68" t="n">
-        <v>7171616</v>
+        <v>7171690</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8180,11 +8179,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8203,17 +8197,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014526</v>
+        <v>125014301</v>
       </c>
       <c r="B69" t="n">
-        <v>78834</v>
+        <v>98269</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8222,34 +8216,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8257,10 +8252,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810999</v>
+        <v>810839</v>
       </c>
       <c r="R69" t="n">
-        <v>7171690</v>
+        <v>7171616</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8295,6 +8290,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014750</v>
+        <v>125014622</v>
       </c>
       <c r="B25" t="n">
         <v>98269</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810464</v>
+        <v>810448</v>
       </c>
       <c r="R25" t="n">
-        <v>7171463</v>
+        <v>7171471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,6 +3346,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3364,14 +3369,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014705</v>
+        <v>125014750</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810458</v>
+        <v>810464</v>
       </c>
       <c r="R26" t="n">
-        <v>7171462</v>
+        <v>7171463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,7 +3487,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014622</v>
+        <v>125014705</v>
       </c>
       <c r="B27" t="n">
         <v>98269</v>
@@ -3530,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810448</v>
+        <v>810458</v>
       </c>
       <c r="R27" t="n">
-        <v>7171471</v>
+        <v>7171462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,11 +3573,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014526</v>
+        <v>125014301</v>
       </c>
       <c r="B68" t="n">
-        <v>78971</v>
+        <v>98269</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8106,34 +8106,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8141,10 +8142,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810999</v>
+        <v>810839</v>
       </c>
       <c r="R68" t="n">
-        <v>7171690</v>
+        <v>7171616</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8179,6 +8180,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8197,17 +8203,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014301</v>
+        <v>125014526</v>
       </c>
       <c r="B69" t="n">
-        <v>98269</v>
+        <v>78971</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8216,35 +8222,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8252,10 +8257,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810839</v>
+        <v>810999</v>
       </c>
       <c r="R69" t="n">
-        <v>7171616</v>
+        <v>7171690</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8290,11 +8295,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -1689,11 +1689,6 @@
       <c r="B11" t="n">
         <v>57635</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2255,11 +2250,6 @@
       <c r="B16" t="n">
         <v>57635</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3260,15 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B25" t="n">
         <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R25" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,11 +3331,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3369,22 +3349,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014750</v>
+        <v>125014622</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3424,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810464</v>
+        <v>810448</v>
       </c>
       <c r="R26" t="n">
-        <v>7171463</v>
+        <v>7171471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,6 +3437,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,7 +3460,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3492,11 +3472,6 @@
       <c r="B27" t="n">
         <v>98269</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>VU</t>
@@ -3603,11 +3578,6 @@
       <c r="B28" t="n">
         <v>98269</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>VU</t>
@@ -4943,11 +4913,6 @@
       </c>
       <c r="B40" t="n">
         <v>57635</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5734,11 +5699,6 @@
       <c r="B47" t="n">
         <v>57635</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6187,11 +6147,6 @@
       </c>
       <c r="B51" t="n">
         <v>57635</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8094,47 +8049,41 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014301</v>
+        <v>125014526</v>
       </c>
       <c r="B68" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78971</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8142,10 +8091,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810839</v>
+        <v>810999</v>
       </c>
       <c r="R68" t="n">
-        <v>7171616</v>
+        <v>7171690</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8180,11 +8129,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8203,53 +8147,49 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014526</v>
+        <v>125014301</v>
       </c>
       <c r="B69" t="n">
-        <v>78971</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8257,10 +8197,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810999</v>
+        <v>810839</v>
       </c>
       <c r="R69" t="n">
-        <v>7171690</v>
+        <v>7171616</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8295,6 +8235,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8313,7 +8258,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,53 +3679,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>391091</v>
+        <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810860.7270867341</v>
+        <v>810449</v>
       </c>
       <c r="R29" t="n">
-        <v>7171669.623737417</v>
+        <v>7171467</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3749,22 +3752,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,6 +3766,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3791,53 +3785,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2055139</v>
+        <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>78097</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810860.7270867341</v>
+        <v>810446</v>
       </c>
       <c r="R30" t="n">
-        <v>7171669.623737417</v>
+        <v>7171459</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3861,22 +3858,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,10 +3872,10 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AR30" t="inlineStr"/>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -3904,10 +3891,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>292476</v>
+        <v>391091</v>
       </c>
       <c r="B31" t="n">
-        <v>79432</v>
+        <v>81235</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3920,34 +3907,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tallskog Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810917.5546458759</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R31" t="n">
-        <v>7171682.39060352</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3974,7 +3961,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -3984,17 +3971,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2007-10-31</t>
+          <t>2007-12-31</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>rapport från Patrik Nygren, SNF</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4009,22 +3991,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>292265</v>
+        <v>2055139</v>
       </c>
       <c r="B32" t="n">
-        <v>79432</v>
+        <v>78097</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4037,21 +4019,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4091,7 +4073,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4134,10 +4116,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650329</v>
+        <v>292476</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79432</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4150,44 +4132,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>Tallskog Storön, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810886</v>
+        <v>810917.5546458759</v>
       </c>
       <c r="R33" t="n">
-        <v>7171642</v>
+        <v>7171682.39060352</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4211,12 +4186,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-10-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>rapport från Patrik Nygren, SNF</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4225,29 +4215,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Via Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650264</v>
+        <v>292265</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79432</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4260,44 +4249,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811045</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R34" t="n">
-        <v>7171680</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4321,12 +4303,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4335,10 +4327,10 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AR34" t="inlineStr"/>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4354,7 +4346,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650270</v>
+        <v>122650329</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4401,10 +4393,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811036</v>
+        <v>810886</v>
       </c>
       <c r="R35" t="n">
-        <v>7171698</v>
+        <v>7171642</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4464,7 +4456,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650066</v>
+        <v>122650264</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4511,10 +4503,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810939</v>
+        <v>811045</v>
       </c>
       <c r="R36" t="n">
-        <v>7171504</v>
+        <v>7171680</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4574,7 +4566,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122649988</v>
+        <v>122650270</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4621,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810939</v>
+        <v>811036</v>
       </c>
       <c r="R37" t="n">
-        <v>7171498</v>
+        <v>7171698</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4684,7 +4676,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122649921</v>
+        <v>122650066</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4731,10 +4723,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810786</v>
+        <v>810939</v>
       </c>
       <c r="R38" t="n">
-        <v>7171426</v>
+        <v>7171504</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4794,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122650277</v>
+        <v>122649988</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4810,31 +4802,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4842,10 +4833,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811014</v>
+        <v>810939</v>
       </c>
       <c r="R39" t="n">
-        <v>7171734</v>
+        <v>7171498</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4880,17 +4871,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4909,10 +4896,15 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122650339</v>
+        <v>122649921</v>
       </c>
       <c r="B40" t="n">
-        <v>57635</v>
+        <v>78766</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,27 +4912,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4948,10 +4943,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810833</v>
+        <v>810786</v>
       </c>
       <c r="R40" t="n">
-        <v>7171605</v>
+        <v>7171426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4986,17 +4981,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5015,10 +5006,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122649892</v>
+        <v>122650277</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5031,30 +5022,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5062,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810633</v>
+        <v>811014</v>
       </c>
       <c r="R41" t="n">
-        <v>7171420</v>
+        <v>7171734</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5100,13 +5092,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5125,15 +5121,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122650292</v>
+        <v>122650339</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,30 +5132,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5172,10 +5160,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810931</v>
+        <v>810833</v>
       </c>
       <c r="R42" t="n">
-        <v>7171669</v>
+        <v>7171605</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5210,13 +5198,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5235,7 +5227,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122650350</v>
+        <v>122649892</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -5282,10 +5274,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810833</v>
+        <v>810633</v>
       </c>
       <c r="R43" t="n">
-        <v>7171605</v>
+        <v>7171420</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5345,10 +5337,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122649934</v>
+        <v>122650292</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5361,31 +5353,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5393,10 +5384,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810828</v>
+        <v>810931</v>
       </c>
       <c r="R44" t="n">
-        <v>7171441</v>
+        <v>7171669</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5431,17 +5422,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5460,10 +5447,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122650318</v>
+        <v>122650350</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5476,31 +5463,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5508,10 +5494,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810936</v>
+        <v>810833</v>
       </c>
       <c r="R45" t="n">
-        <v>7171645</v>
+        <v>7171605</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5546,17 +5532,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>två stora bohål i ihålig gammeltall</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5575,10 +5557,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123105448</v>
+        <v>122649934</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5591,32 +5573,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5626,10 +5605,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810833</v>
+        <v>810828</v>
       </c>
       <c r="R46" t="n">
-        <v>7171608</v>
+        <v>7171441</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5656,17 +5635,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
+          <t>äldre ringhack i gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5675,7 +5654,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5694,10 +5672,15 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123107459</v>
+        <v>122650318</v>
       </c>
       <c r="B47" t="n">
-        <v>57635</v>
+        <v>57494</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5705,16 +5688,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5727,7 +5710,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5737,10 +5720,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811055</v>
+        <v>810936</v>
       </c>
       <c r="R47" t="n">
-        <v>7171672</v>
+        <v>7171645</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5767,17 +5750,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>två stora bohål i ihålig gammeltall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5804,7 +5787,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123105526</v>
+        <v>123105448</v>
       </c>
       <c r="B48" t="n">
         <v>78788</v>
@@ -5843,7 +5826,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5851,10 +5838,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810798</v>
+        <v>810833</v>
       </c>
       <c r="R48" t="n">
-        <v>7171573</v>
+        <v>7171608</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5887,6 +5874,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5914,15 +5906,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107351</v>
+        <v>123107459</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,32 +5917,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5965,10 +5949,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811003</v>
+        <v>811055</v>
       </c>
       <c r="R49" t="n">
-        <v>7171721</v>
+        <v>7171672</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6005,7 +5989,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6014,7 +5998,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6033,7 +6016,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123113230</v>
+        <v>123105526</v>
       </c>
       <c r="B50" t="n">
         <v>78788</v>
@@ -6080,10 +6063,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810850</v>
+        <v>810798</v>
       </c>
       <c r="R50" t="n">
-        <v>7171671</v>
+        <v>7171573</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6143,10 +6126,15 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123113132</v>
+        <v>123107351</v>
       </c>
       <c r="B51" t="n">
-        <v>57635</v>
+        <v>78788</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6154,29 +6142,32 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6186,10 +6177,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810895</v>
+        <v>811003</v>
       </c>
       <c r="R51" t="n">
-        <v>7171694</v>
+        <v>7171721</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6226,7 +6217,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6235,6 +6226,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6253,10 +6245,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123113205</v>
+        <v>123113230</v>
       </c>
       <c r="B52" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6269,21 +6261,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6300,10 +6292,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810862</v>
+        <v>810850</v>
       </c>
       <c r="R52" t="n">
-        <v>7171664</v>
+        <v>7171671</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6363,15 +6355,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123107500</v>
+        <v>123113132</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6379,30 +6366,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6410,10 +6398,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811043</v>
+        <v>810895</v>
       </c>
       <c r="R53" t="n">
-        <v>7171704</v>
+        <v>7171694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6448,13 +6436,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6473,10 +6465,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123113317</v>
+        <v>123113205</v>
       </c>
       <c r="B54" t="n">
-        <v>57507</v>
+        <v>78820</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6489,31 +6481,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6521,10 +6512,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810707</v>
+        <v>810862</v>
       </c>
       <c r="R54" t="n">
-        <v>7171592</v>
+        <v>7171664</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6559,17 +6550,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>hål i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6588,7 +6575,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107487</v>
+        <v>123107500</v>
       </c>
       <c r="B55" t="n">
         <v>78788</v>
@@ -6635,10 +6622,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811052</v>
+        <v>811043</v>
       </c>
       <c r="R55" t="n">
-        <v>7171679</v>
+        <v>7171704</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6671,11 +6658,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6703,10 +6685,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123113174</v>
+        <v>123113317</v>
       </c>
       <c r="B56" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6719,30 +6701,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6750,10 +6733,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810865</v>
+        <v>810707</v>
       </c>
       <c r="R56" t="n">
-        <v>7171668</v>
+        <v>7171592</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6790,7 +6773,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>hänglavrikt bla garnlav</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6799,7 +6782,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6818,10 +6800,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123105541</v>
+        <v>123107487</v>
       </c>
       <c r="B57" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6830,25 +6812,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6865,10 +6847,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810786</v>
+        <v>811052</v>
       </c>
       <c r="R57" t="n">
-        <v>7171568</v>
+        <v>7171679</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6901,6 +6883,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6928,10 +6915,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123107426</v>
+        <v>123113174</v>
       </c>
       <c r="B58" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6944,27 +6931,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6972,10 +6962,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811024</v>
+        <v>810865</v>
       </c>
       <c r="R58" t="n">
-        <v>7171733</v>
+        <v>7171668</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7012,7 +7002,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7021,6 +7011,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7039,10 +7030,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107409</v>
+        <v>123105541</v>
       </c>
       <c r="B59" t="n">
-        <v>57491</v>
+        <v>78812</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7051,35 +7042,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7087,10 +7077,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811024</v>
+        <v>810786</v>
       </c>
       <c r="R59" t="n">
-        <v>7171733</v>
+        <v>7171568</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7125,17 +7115,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7154,10 +7140,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123107511</v>
+        <v>123107426</v>
       </c>
       <c r="B60" t="n">
-        <v>78812</v>
+        <v>57507</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7166,34 +7152,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7201,10 +7184,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811066</v>
+        <v>811024</v>
       </c>
       <c r="R60" t="n">
-        <v>7171715</v>
+        <v>7171733</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7239,13 +7222,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7264,10 +7251,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107538</v>
+        <v>123107409</v>
       </c>
       <c r="B61" t="n">
-        <v>78812</v>
+        <v>57491</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7276,34 +7263,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7311,10 +7299,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>810978</v>
+        <v>811024</v>
       </c>
       <c r="R61" t="n">
-        <v>7171744</v>
+        <v>7171733</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7349,13 +7337,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7374,10 +7366,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123113295</v>
+        <v>123107511</v>
       </c>
       <c r="B62" t="n">
-        <v>57507</v>
+        <v>78812</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7386,35 +7378,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7422,10 +7413,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810851</v>
+        <v>811066</v>
       </c>
       <c r="R62" t="n">
-        <v>7171663</v>
+        <v>7171715</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7460,17 +7451,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7489,10 +7476,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123107589</v>
+        <v>123107538</v>
       </c>
       <c r="B63" t="n">
-        <v>82575</v>
+        <v>78812</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7501,31 +7488,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -7536,10 +7523,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>810886</v>
+        <v>810978</v>
       </c>
       <c r="R63" t="n">
-        <v>7171705</v>
+        <v>7171744</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7599,10 +7586,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123107525</v>
+        <v>123113295</v>
       </c>
       <c r="B64" t="n">
-        <v>78812</v>
+        <v>57507</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7611,34 +7598,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7646,10 +7634,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811018</v>
+        <v>810851</v>
       </c>
       <c r="R64" t="n">
-        <v>7171753</v>
+        <v>7171663</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7684,13 +7672,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7709,10 +7701,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123105488</v>
+        <v>123107589</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7725,27 +7717,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -7756,10 +7748,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>810824</v>
+        <v>810886</v>
       </c>
       <c r="R65" t="n">
-        <v>7171598</v>
+        <v>7171705</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7792,11 +7784,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7824,10 +7811,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123107271</v>
+        <v>123107525</v>
       </c>
       <c r="B66" t="n">
-        <v>57507</v>
+        <v>78812</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7836,35 +7823,34 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7872,10 +7858,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>810992</v>
+        <v>811018</v>
       </c>
       <c r="R66" t="n">
-        <v>7171739</v>
+        <v>7171753</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7910,17 +7896,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7939,7 +7921,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123107580</v>
+        <v>123105488</v>
       </c>
       <c r="B67" t="n">
         <v>78788</v>
@@ -7986,10 +7968,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>810886</v>
+        <v>810824</v>
       </c>
       <c r="R67" t="n">
-        <v>7171705</v>
+        <v>7171598</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8022,6 +8004,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8049,41 +8036,47 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014526</v>
+        <v>123107271</v>
       </c>
       <c r="B68" t="n">
-        <v>78971</v>
+        <v>57507</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8091,10 +8084,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810999</v>
+        <v>810992</v>
       </c>
       <c r="R68" t="n">
-        <v>7171690</v>
+        <v>7171739</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8121,12 +8114,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8135,7 +8133,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8154,42 +8151,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014301</v>
+        <v>123107580</v>
       </c>
       <c r="B69" t="n">
-        <v>98269</v>
+        <v>78788</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8197,10 +8198,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810839</v>
+        <v>810886</v>
       </c>
       <c r="R69" t="n">
-        <v>7171616</v>
+        <v>7171705</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8227,17 +8228,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8258,10 +8254,226 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125014526</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78971</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>810999</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7171690</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125014301</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>810839</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7171616</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
           <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3682,7 +3682,7 @@
         <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3682,7 +3682,7 @@
         <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3682,7 +3682,7 @@
         <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3682,7 +3682,7 @@
         <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3682,7 +3682,7 @@
         <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3682,7 +3682,7 @@
         <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3682,7 +3682,7 @@
         <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -3682,7 +3682,7 @@
         <v>127646386</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127646430</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 18574-2025 artfynd.xlsx
+++ b/artfynd/A 18574-2025 artfynd.xlsx
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
@@ -5996,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG49" t="b">
         <v>0</v>
@@ -6445,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="AE53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG53" t="b">
         <v>0</v>
